--- a/backend/src/main/resources/data/청년정책_final_data.xlsx
+++ b/backend/src/main/resources/data/청년정책_final_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeonsangmin/Desktop/공모전/backend/src/main/resources/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38628701-F5C9-7D4E-B238-AD3EB5E0B54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB706854-A91F-064A-8F67-B82CDEF6128C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13219" uniqueCount="3628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13127" uniqueCount="3627">
   <si>
     <t>정책명</t>
   </si>
@@ -14129,65 +14129,61 @@
     <t>문의:  02-2241-3996</t>
   </si>
   <si>
-    <t>테스트 청년 정책 알림 확인</t>
-  </si>
-  <si>
-    <t>TEST_POLICY_001</t>
-  </si>
-  <si>
-    <t>일자리</t>
-  </si>
-  <si>
-    <t>테스트,알림,청년</t>
-  </si>
-  <si>
-    <t>알림 기능 테스트를 위한 정책입니다.</t>
-  </si>
-  <si>
-    <t>테스트 대상 청년에게 정책 정보를 제공합니다.</t>
-  </si>
-  <si>
-    <t>테스트 사업기간</t>
-  </si>
-  <si>
-    <t>소득 제한 없음</t>
-  </si>
-  <si>
-    <t>테스트용 추가 조건 없음</t>
-  </si>
-  <si>
-    <t>제한 없음</t>
-  </si>
-  <si>
-    <t>내부 심사</t>
-  </si>
-  <si>
-    <t>해당 없음</t>
-  </si>
-  <si>
-    <t>https://www.example.com</t>
-  </si>
-  <si>
-    <t>알림 기능 테스트용 데이터입니다.</t>
-  </si>
-  <si>
-    <t>https://www.example.com/ref1</t>
-  </si>
-  <si>
-    <t>https://www.example.com/ref2</t>
-  </si>
-  <si>
-    <t>TEST_POLICY_002</t>
-  </si>
-  <si>
-    <t>TEST_POLICY_003</t>
-  </si>
-  <si>
-    <t>TEST_POLICY_004</t>
-  </si>
-  <si>
-    <t>TEST_POLICY_005</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>REAL_POLICY_001</t>
+  </si>
+  <si>
+    <t>금융</t>
+  </si>
+  <si>
+    <t>저축,자산형성,근로청년</t>
+  </si>
+  <si>
+    <t>일하는 청년의 자산 형성을 지원하는 정책입니다.</t>
+  </si>
+  <si>
+    <t>근로 중인 청년이 매월 일정 금액을 저축하면 정부가 추가 지원금을 적립해 목돈 마련을 지원합니다.</t>
+  </si>
+  <si>
+    <t>연중 모집</t>
+  </si>
+  <si>
+    <t>기준 중위소득 100% 이하</t>
+  </si>
+  <si>
+    <t>근로중인 청년</t>
+  </si>
+  <si>
+    <t>월 소득 기준 충족 필요</t>
+  </si>
+  <si>
+    <t>기초생활수급자 및 차상위 우대</t>
+  </si>
+  <si>
+    <t>가구 기준 충족 필요</t>
+  </si>
+  <si>
+    <t>근로 및 소득 조건 충족 필요</t>
+  </si>
+  <si>
+    <t>군 복무 기간 일부 연령 계산 제외</t>
+  </si>
+  <si>
+    <t>복지로 온라인 신청</t>
+  </si>
+  <si>
+    <t>서류 심사 및 자격 검증</t>
+  </si>
+  <si>
+    <t>신분증, 소득 증빙서류</t>
+  </si>
+  <si>
+    <t>청년의 자산 형성과 경제적 자립을 위한 정부 지원 사업입니다.</t>
+  </si>
+  <si>
+    <t>https://www.moel.go.kr</t>
+  </si>
+  <si>
+    <t>https://www.korea.kr</t>
   </si>
 </sst>
 </file>
@@ -14611,7 +14607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC529"/>
+  <dimension ref="A1:AC530"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -61266,45 +61262,45 @@
         <v>46</v>
       </c>
     </row>
-    <row r="525" spans="1:29">
+    <row r="525" spans="1:29" ht="30">
       <c r="A525" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B525" t="s">
         <v>3608</v>
       </c>
-      <c r="B525" t="s">
+      <c r="C525" t="s">
         <v>3609</v>
       </c>
-      <c r="C525" t="s">
+      <c r="D525" t="s">
         <v>3610</v>
       </c>
-      <c r="D525" t="s">
+      <c r="E525" t="s">
         <v>3611</v>
       </c>
-      <c r="E525" t="s">
+      <c r="F525" t="s">
         <v>3612</v>
       </c>
-      <c r="F525" t="s">
+      <c r="G525" s="5">
+        <v>46023</v>
+      </c>
+      <c r="H525" s="5">
+        <v>46387</v>
+      </c>
+      <c r="I525" s="5">
+        <v>46023</v>
+      </c>
+      <c r="J525" s="5">
+        <v>46387</v>
+      </c>
+      <c r="K525" t="s">
         <v>3613</v>
-      </c>
-      <c r="G525">
-        <v>20260506</v>
-      </c>
-      <c r="H525">
-        <v>20261231</v>
-      </c>
-      <c r="I525">
-        <v>20260506</v>
-      </c>
-      <c r="J525">
-        <v>20261231</v>
-      </c>
-      <c r="K525" t="s">
-        <v>3614</v>
       </c>
       <c r="L525" t="s">
         <v>441</v>
       </c>
       <c r="M525" s="6" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="N525" t="s">
         <v>39</v>
@@ -61316,400 +61312,61 @@
         <v>34</v>
       </c>
       <c r="Q525" t="s">
-        <v>39</v>
+        <v>3615</v>
       </c>
       <c r="R525" t="s">
-        <v>39</v>
+        <v>3616</v>
       </c>
       <c r="S525" t="s">
-        <v>39</v>
+        <v>3617</v>
       </c>
       <c r="T525" t="s">
-        <v>39</v>
+        <v>3618</v>
       </c>
       <c r="U525" t="s">
-        <v>3616</v>
+        <v>3619</v>
       </c>
       <c r="V525" t="s">
-        <v>3617</v>
+        <v>3620</v>
       </c>
       <c r="W525" t="s">
-        <v>1105</v>
+        <v>3621</v>
       </c>
       <c r="X525" t="s">
-        <v>3618</v>
+        <v>3622</v>
       </c>
       <c r="Y525" t="s">
-        <v>3619</v>
+        <v>3623</v>
       </c>
       <c r="Z525" t="s">
-        <v>3620</v>
+        <v>414</v>
       </c>
       <c r="AA525" t="s">
-        <v>3621</v>
+        <v>3624</v>
       </c>
       <c r="AB525" t="s">
-        <v>3622</v>
+        <v>3625</v>
       </c>
       <c r="AC525" t="s">
-        <v>3623</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="526" spans="1:29">
-      <c r="A526" t="s">
-        <v>3608</v>
-      </c>
-      <c r="B526" t="s">
-        <v>3624</v>
-      </c>
-      <c r="C526" t="s">
-        <v>3610</v>
-      </c>
-      <c r="D526" t="s">
-        <v>3611</v>
-      </c>
-      <c r="E526" t="s">
-        <v>3612</v>
-      </c>
-      <c r="F526" t="s">
-        <v>3613</v>
-      </c>
-      <c r="G526">
-        <v>20260506</v>
-      </c>
-      <c r="H526">
-        <v>20261231</v>
-      </c>
-      <c r="I526">
-        <v>20260506</v>
-      </c>
-      <c r="J526">
-        <v>20261231</v>
-      </c>
-      <c r="K526" t="s">
-        <v>3614</v>
-      </c>
-      <c r="L526" t="s">
-        <v>441</v>
-      </c>
-      <c r="M526" s="6" t="s">
-        <v>3615</v>
-      </c>
-      <c r="N526" t="s">
-        <v>39</v>
-      </c>
-      <c r="O526">
-        <v>19</v>
-      </c>
-      <c r="P526">
-        <v>34</v>
-      </c>
-      <c r="Q526" t="s">
-        <v>39</v>
-      </c>
-      <c r="R526" t="s">
-        <v>39</v>
-      </c>
-      <c r="S526" t="s">
-        <v>39</v>
-      </c>
-      <c r="T526" t="s">
-        <v>39</v>
-      </c>
-      <c r="U526" t="s">
-        <v>3616</v>
-      </c>
-      <c r="V526" t="s">
-        <v>3617</v>
-      </c>
-      <c r="W526" t="s">
-        <v>1105</v>
-      </c>
-      <c r="X526" t="s">
-        <v>3618</v>
-      </c>
-      <c r="Y526" t="s">
-        <v>3619</v>
-      </c>
-      <c r="Z526" t="s">
-        <v>3620</v>
-      </c>
-      <c r="AA526" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AB526" t="s">
-        <v>3622</v>
-      </c>
-      <c r="AC526" t="s">
-        <v>3623</v>
-      </c>
+      <c r="M526" s="6"/>
     </row>
     <row r="527" spans="1:29">
-      <c r="A527" t="s">
-        <v>3608</v>
-      </c>
-      <c r="B527" t="s">
-        <v>3625</v>
-      </c>
-      <c r="C527" t="s">
-        <v>3610</v>
-      </c>
-      <c r="D527" t="s">
-        <v>3611</v>
-      </c>
-      <c r="E527" t="s">
-        <v>3612</v>
-      </c>
-      <c r="F527" t="s">
-        <v>3613</v>
-      </c>
-      <c r="G527">
-        <v>20260506</v>
-      </c>
-      <c r="H527">
-        <v>20261231</v>
-      </c>
-      <c r="I527">
-        <v>20260506</v>
-      </c>
-      <c r="J527">
-        <v>20261231</v>
-      </c>
-      <c r="K527" t="s">
-        <v>3614</v>
-      </c>
-      <c r="L527" t="s">
-        <v>441</v>
-      </c>
-      <c r="M527" s="6" t="s">
-        <v>3615</v>
-      </c>
-      <c r="N527" t="s">
-        <v>39</v>
-      </c>
-      <c r="O527">
-        <v>19</v>
-      </c>
-      <c r="P527">
-        <v>34</v>
-      </c>
-      <c r="Q527" t="s">
-        <v>39</v>
-      </c>
-      <c r="R527" t="s">
-        <v>39</v>
-      </c>
-      <c r="S527" t="s">
-        <v>39</v>
-      </c>
-      <c r="T527" t="s">
-        <v>39</v>
-      </c>
-      <c r="U527" t="s">
-        <v>3616</v>
-      </c>
-      <c r="V527" t="s">
-        <v>3617</v>
-      </c>
-      <c r="W527" t="s">
-        <v>1105</v>
-      </c>
-      <c r="X527" t="s">
-        <v>3618</v>
-      </c>
-      <c r="Y527" t="s">
-        <v>3619</v>
-      </c>
-      <c r="Z527" t="s">
-        <v>3620</v>
-      </c>
-      <c r="AA527" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AB527" t="s">
-        <v>3622</v>
-      </c>
-      <c r="AC527" t="s">
-        <v>3623</v>
-      </c>
+      <c r="M527" s="6"/>
     </row>
     <row r="528" spans="1:29">
-      <c r="A528" t="s">
-        <v>3608</v>
-      </c>
-      <c r="B528" t="s">
-        <v>3626</v>
-      </c>
-      <c r="C528" t="s">
-        <v>3610</v>
-      </c>
-      <c r="D528" t="s">
-        <v>3611</v>
-      </c>
-      <c r="E528" t="s">
-        <v>3612</v>
-      </c>
-      <c r="F528" t="s">
-        <v>3613</v>
-      </c>
-      <c r="G528">
-        <v>20260506</v>
-      </c>
-      <c r="H528">
-        <v>20261231</v>
-      </c>
-      <c r="I528">
-        <v>20260506</v>
-      </c>
-      <c r="J528">
-        <v>20261231</v>
-      </c>
-      <c r="K528" t="s">
-        <v>3614</v>
-      </c>
-      <c r="L528" t="s">
-        <v>441</v>
-      </c>
-      <c r="M528" s="6" t="s">
-        <v>3615</v>
-      </c>
-      <c r="N528" t="s">
-        <v>39</v>
-      </c>
-      <c r="O528">
-        <v>19</v>
-      </c>
-      <c r="P528">
-        <v>34</v>
-      </c>
-      <c r="Q528" t="s">
-        <v>39</v>
-      </c>
-      <c r="R528" t="s">
-        <v>39</v>
-      </c>
-      <c r="S528" t="s">
-        <v>39</v>
-      </c>
-      <c r="T528" t="s">
-        <v>39</v>
-      </c>
-      <c r="U528" t="s">
-        <v>3616</v>
-      </c>
-      <c r="V528" t="s">
-        <v>3617</v>
-      </c>
-      <c r="W528" t="s">
-        <v>1105</v>
-      </c>
-      <c r="X528" t="s">
-        <v>3618</v>
-      </c>
-      <c r="Y528" t="s">
-        <v>3619</v>
-      </c>
-      <c r="Z528" t="s">
-        <v>3620</v>
-      </c>
-      <c r="AA528" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AB528" t="s">
-        <v>3622</v>
-      </c>
-      <c r="AC528" t="s">
-        <v>3623</v>
-      </c>
+      <c r="M528" s="6"/>
     </row>
-    <row r="529" spans="1:29">
-      <c r="A529" t="s">
-        <v>3608</v>
-      </c>
-      <c r="B529" t="s">
-        <v>3627</v>
-      </c>
-      <c r="C529" t="s">
-        <v>3610</v>
-      </c>
-      <c r="D529" t="s">
-        <v>3611</v>
-      </c>
-      <c r="E529" t="s">
-        <v>3612</v>
-      </c>
-      <c r="F529" t="s">
-        <v>3613</v>
-      </c>
-      <c r="G529">
-        <v>20260506</v>
-      </c>
-      <c r="H529">
-        <v>20261231</v>
-      </c>
-      <c r="I529">
-        <v>20260506</v>
-      </c>
-      <c r="J529">
-        <v>20261231</v>
-      </c>
-      <c r="K529" t="s">
-        <v>3614</v>
-      </c>
-      <c r="L529" s="4" t="s">
-        <v>3555</v>
-      </c>
-      <c r="M529" s="6" t="s">
-        <v>3615</v>
-      </c>
-      <c r="N529" t="s">
-        <v>39</v>
-      </c>
-      <c r="O529">
-        <v>19</v>
-      </c>
-      <c r="P529">
-        <v>34</v>
-      </c>
-      <c r="Q529" t="s">
-        <v>39</v>
-      </c>
-      <c r="R529" t="s">
-        <v>39</v>
-      </c>
-      <c r="S529" t="s">
-        <v>39</v>
-      </c>
-      <c r="T529" t="s">
-        <v>39</v>
-      </c>
-      <c r="U529" t="s">
-        <v>3616</v>
-      </c>
-      <c r="V529" t="s">
-        <v>3617</v>
-      </c>
-      <c r="W529" t="s">
-        <v>1105</v>
-      </c>
-      <c r="X529" t="s">
-        <v>3618</v>
-      </c>
-      <c r="Y529" t="s">
-        <v>3619</v>
-      </c>
-      <c r="Z529" t="s">
-        <v>3620</v>
-      </c>
-      <c r="AA529" t="s">
-        <v>3621</v>
-      </c>
-      <c r="AB529" t="s">
-        <v>3622</v>
-      </c>
-      <c r="AC529" t="s">
-        <v>3623</v>
-      </c>
+    <row r="529" spans="12:13">
+      <c r="L529" s="4"/>
+      <c r="M529" s="6"/>
+    </row>
+    <row r="530" spans="12:13">
+      <c r="L530" s="2"/>
+      <c r="M530" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
